--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -540,22 +540,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>5.71</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.5</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -572,22 +575,25 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -604,22 +610,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -811,22 +820,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -843,22 +855,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>59.38</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -875,22 +890,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>39.39</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -907,22 +925,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>28.57</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -939,22 +960,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.1</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1747,22 +1771,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>5.71</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.5</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1779,22 +1806,25 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1811,22 +1841,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2018,22 +2051,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2050,22 +2086,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>59.38</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2082,22 +2121,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>39.39</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2114,22 +2156,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>28.57</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2146,22 +2191,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.1</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="15" spans="1:11">

--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -855,25 +855,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>40.63</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>59.38</v>
+        <v>12.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>59.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -890,25 +890,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>39.39</v>
+        <v>18.18</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -925,25 +925,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>71.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H13" s="1">
-        <v>28.57</v>
+        <v>2.86</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -960,25 +960,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H14" s="1">
-        <v>18.18</v>
+        <v>3.03</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -995,22 +995,25 @@
         <v>37</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F15">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1027,22 +1030,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.9</v>
       </c>
       <c r="J16">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1059,22 +1065,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.5</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1091,22 +1100,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
   </sheetData>
@@ -2086,25 +2098,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>40.63</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>59.38</v>
+        <v>12.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>59.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2121,25 +2133,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>39.39</v>
+        <v>18.18</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2156,25 +2168,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>71.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H13" s="1">
-        <v>28.57</v>
+        <v>2.86</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2191,25 +2203,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H14" s="1">
-        <v>18.18</v>
+        <v>3.03</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2226,22 +2238,25 @@
         <v>37</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F15">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2258,22 +2273,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.9</v>
       </c>
       <c r="J16">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2290,22 +2308,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.5</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2322,22 +2343,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -537,28 +537,28 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>33</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H2" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
       <c r="I2" s="2">
         <v>9.5</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -747,28 +747,28 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>26</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H8" s="1">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
       <c r="K8" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -797,13 +797,13 @@
         <v>11.43</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -922,22 +922,22 @@
         <v>33</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>34</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -992,28 +992,28 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>33</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="H15" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
       <c r="I15" s="2">
         <v>9</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1030,25 +1030,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1184,13 +1184,13 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>100</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1315,22 +1315,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>24.24</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1347,22 +1350,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>29.03</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>70.97</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1376,25 +1382,28 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1411,22 +1420,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1475,22 +1487,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1507,22 +1522,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>24.24</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1536,25 +1554,28 @@
         <v>33</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>14.71</v>
+      </c>
+      <c r="I13" s="2">
+        <v>9.5</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1571,22 +1592,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>6.06</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.6</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1600,25 +1624,28 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F15">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1780,28 +1807,28 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>33</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H2" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
       <c r="I2" s="2">
         <v>9.5</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1935,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1970,7 +1997,7 @@
         <v>16.13</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1990,19 +2017,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2">
         <v>8.4</v>
@@ -2011,7 +2038,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2028,25 +2055,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2098,19 +2125,19 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>3.13</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2133,19 +2160,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>18.18</v>
+        <v>15.15</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2165,22 +2192,22 @@
         <v>33</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>34</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2203,19 +2230,19 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2235,28 +2262,28 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>33</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="H15" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
       <c r="I15" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2273,25 +2300,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">

--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -540,25 +540,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4.17</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1100,25 +1100,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K18" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
     </row>
   </sheetData>
@@ -1187,22 +1187,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.6</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1219,22 +1222,25 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.5</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1251,22 +1257,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>3.23</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1283,22 +1292,25 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1455,22 +1467,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1487,25 +1502,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>75</v>
+        <v>84.38</v>
       </c>
       <c r="H11" s="1">
-        <v>25</v>
+        <v>15.63</v>
       </c>
       <c r="I11" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1534,13 +1549,13 @@
         <v>24.24</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>15.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1557,25 +1572,25 @@
         <v>34</v>
       </c>
       <c r="E13">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>85.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1592,25 +1607,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1662,22 +1677,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1694,22 +1712,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1726,22 +1747,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>31.58</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>31.58</v>
       </c>
     </row>
   </sheetData>
@@ -1810,25 +1834,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1857,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1880,19 +1904,19 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1915,25 +1939,25 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="H5" s="1">
-        <v>4.17</v>
+        <v>8.33</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2125,19 +2149,19 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>96.88</v>
+        <v>84.38</v>
       </c>
       <c r="H11" s="1">
-        <v>3.13</v>
+        <v>15.63</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2160,19 +2184,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>84.84999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>15.15</v>
+        <v>24.24</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2207,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2242,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2312,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2335,19 +2359,19 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H17" s="1">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I17" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -2370,25 +2394,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K18" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>8.33</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2149,19 +2149,19 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="H11" s="1">
-        <v>15.63</v>
+        <v>3.13</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2184,19 +2184,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>75.76000000000001</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>24.24</v>
+        <v>21.21</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J14">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20212.xlsx
+++ b/academias/Biología - Estadisticos 20212.xlsx
@@ -715,25 +715,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>83.87</v>
+        <v>93.55</v>
       </c>
       <c r="H7" s="1">
-        <v>16.13</v>
+        <v>6.45</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -750,25 +750,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -785,25 +785,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>11.43</v>
+        <v>5.71</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -995,25 +995,25 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>9</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1065,25 +1065,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H17" s="1">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I17" s="2">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1100,25 +1100,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H18" s="1">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="I18" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1327,25 +1327,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>75.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="H6" s="1">
-        <v>24.24</v>
+        <v>6.06</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>24.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1362,25 +1362,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>29.03</v>
+        <v>77.42</v>
       </c>
       <c r="H7" s="1">
-        <v>70.97</v>
+        <v>22.58</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>70.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1397,25 +1397,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1432,25 +1432,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>80</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>20</v>
+        <v>5.71</v>
       </c>
       <c r="I9" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1642,25 +1642,25 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1677,25 +1677,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1712,25 +1712,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H17" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I17" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1747,25 +1747,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>68.42</v>
+        <v>89.47</v>
       </c>
       <c r="H18" s="1">
-        <v>31.58</v>
+        <v>10.53</v>
       </c>
       <c r="I18" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>31.58</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2009,25 +2009,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>16.13</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2056,13 +2056,13 @@
         <v>10</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2079,25 +2079,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>91.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H9" s="1">
-        <v>8.57</v>
+        <v>2.86</v>
       </c>
       <c r="I9" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2289,25 +2289,25 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2359,25 +2359,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H17" s="1">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2394,25 +2394,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H18" s="1">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="I18" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
